--- a/Reporte_Oportunidades_InmoData.xlsx
+++ b/Reporte_Oportunidades_InmoData.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,44 +453,44 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Botánico, Palermo</t>
+          <t>Palermo, Capital Federal</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>$ 1.500</t>
+          <t>$ 600.000</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>104 m² tot.4 amb.3 dorm.1 baño</t>
+          <t>75 m² tot.2 amb.1 dorm.1 baño1 coch.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-alquiler-de-departamento-4-ambientes-58540876.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-hermoso-dos-ambientes-58879080.html</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Constitución, Capital Federal</t>
+          <t>Recoleta, Capital Federal</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>$ 250.000</t>
+          <t>$ 750.000</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>23 m² tot.1 amb.1 baño</t>
+          <t>80 m² tot.3 amb.2 dorm.2 baños1 coch.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-alquiler-de-estudios-apto-vivienda-o-uso-profesional-54700534.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-depa-lujo-recoleta-58879176.html</t>
         </is>
       </c>
     </row>
@@ -502,215 +502,215 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>USD 800</t>
+          <t>$ 660.000</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>90 m² tot.3 amb.2 dorm.1 baño</t>
+          <t>32 m² tot.1 amb.1 dorm.1 baño</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-hermoso-3-amb-2-banos.-amoblado.-vista-panoramica-58716582.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-hermoso-monoambiente-de-categoria-en-villa-pueyrredon-58878546.html</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Almagro Norte, Almagro</t>
+          <t>Balvanera, Capital Federal</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>$ 650.000</t>
+          <t>$ 600.000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>45 m² tot.1 amb.1 baño</t>
+          <t>48 m² tot.2 amb.1 dorm.1 baño</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-excelente-monoambiente-con-gran-balcon!-58616142.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-departamento-independencia-2105-58877999.html</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Belgrano, Capital Federal</t>
+          <t>Villa Urquiza, Capital Federal</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>USD 1.100</t>
+          <t>$ 600.000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>95 m² tot.4 amb.3 dorm.1 baño1 coch.</t>
+          <t>39 m² tot.1 amb.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-dueno-alquila-v-del-pino-al-2600-seguridad-24hs-55741994.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-monoambiente-en-alquiler-en-villa-urquiza!-58877922.html</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Recoleta, Capital Federal</t>
+          <t>Las Cañitas, Palermo</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>$ 650.000</t>
+          <t>USD 650</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>70 m² tot.2 amb.1 dorm.1 baño1 coch.</t>
+          <t>38 m² tot.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa--universitario-busco-inquilino-responsable-ingreso-58716044.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-jorge-newbery-1764-y-arce-58874045.html</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Recoleta, Capital Federal</t>
+          <t>Botánico, Palermo</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>$ 450</t>
+          <t>$ 600.000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>68 m² tot.2 amb.1 dorm.1 baño1 coch.</t>
+          <t>32 m² tot.1 amb.1 dorm.1 baño</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-departamento-dos-ambientes-58715879.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-alquiler-dueno-directo-en-palermo-58877849.html</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Recoleta, Capital Federal</t>
+          <t>Las Cañitas, Palermo</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>$ 450.000</t>
+          <t>USD 650</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>68 m² tot.2 amb.1 dorm.1 baño1 coch.</t>
+          <t>35 m² tot.1 amb.1 dorm.1 baño</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-dos-ambientes-58715878.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-alquiler-monoambiente-amoblado-58877525.html</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Palermo, Capital Federal</t>
+          <t>Villa Crespo, Capital Federal</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>USD 500</t>
+          <t>$ 850.000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>115 m² tot.3 amb.2 dorm.2 baños</t>
+          <t>47 m² tot.2 amb.1 dorm.1 baño</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-las-canitas-dueno-directo-precio-paquete-todo-incluido-58715857.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-departamento-2-ambientes-en-villa-crespo-58674105.html</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Recoleta, Capital Federal</t>
+          <t>Retiro, Capital Federal</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>$ 670.000</t>
+          <t>$ 1.400.000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>75 m² tot.3 amb.2 dorm.2 baños2 coch.</t>
+          <t>105 m² tot.4 amb.2 dorm.1 baño</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-departamento-amoblado-3-ambientes-duena-directa-58715850.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-excelente-semipiso-en-recoleta-retiro-58734824.html</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Balvanera, Capital Federal</t>
+          <t>Recoleta, Capital Federal</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>$ 550.000</t>
+          <t>$ 1.050.000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>32 m² tot.1 amb.1 baño</t>
+          <t>53 m² tot.3 amb.2 dorm.1 baño</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-muy-lindo-monoambiente-al-fte-con-balcon-58715842.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-palermo-3-amb-luminoso-alquiler-bajas-exp-58877539.html</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Belgrano R, Belgrano</t>
+          <t>Belgrano Chico, Belgrano</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>$ 600</t>
+          <t>$ 1.000.000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>65 m² tot.2 amb.1 dorm.1 baño1 coch.</t>
+          <t>64 m² tot.1 amb.1 baño</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-departamento-belgrano-58715836.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-amplio-departamento-frente-a-av-libertador-58877431.html</t>
         </is>
       </c>
     </row>
@@ -722,112 +722,112 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>$ 600</t>
+          <t>$ 1.200.000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>65 m² tot.2 amb.1 dorm.1 baño1 coch.</t>
+          <t>57 m² tot.3 amb.2 dorm.1 baño1 coch.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-departamento-recoleta-58715821.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-dueno-alquila-3ambientes-vista-abierta-cochera-58877323.html</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Palermo, Capital Federal</t>
+          <t>Villa Urquiza, Capital Federal</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>$ 700.000</t>
+          <t>$ 830.000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>50 m² tot.1 baño</t>
+          <t>64 m² tot.2 amb.1 dorm.1 baño1 coch.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-hermoso-departamento-con-patio-en-zona-alto-palermo-58715421.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-hermoso-duplex-2-amb.-cochera-cub-opcional.-en-la-53446991.html</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Barrio Norte, Capital Federal</t>
+          <t>Floresta Norte, Floresta</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>$ 700.000</t>
+          <t>$ 650.000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>50 m² tot.2 amb.1 dorm.1 baño</t>
+          <t>63 m² tot.3 amb.2 dorm.1 baño</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-hermoso-departamento-con-patio-en-barrio-norte-58715340.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-departamento-contrafrente-en-planta-baja-58874073.html</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Recoleta, Capital Federal</t>
+          <t>Villa Urquiza, Capital Federal</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>$ 700.000</t>
+          <t>$ 650.000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>50 m² tot.2 amb.1 dorm.1 baño</t>
+          <t>41 m² tot.1 amb.1 baño</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-hermoso-departamento-de-2-ambientes-con-patio-en-58715264.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-hermoso-monoambiente-en-la-zona-mas-estrategica-de-58871227.html</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Recoleta, Capital Federal</t>
+          <t>Palermo Nuevo, Palermo</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>$ 600.000</t>
+          <t>$ 500.000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>30 m² tot.2 amb.1 dorm.1 baño</t>
+          <t>25 m² tot.1 amb.1 baño</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-alquilo-departamento-58715263.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-alquiler-dueno-monoamb-pb-palermo-nuevo-frente-le-parc-58265665.html</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Recoleta, Capital Federal</t>
+          <t>Caballito, Capital Federal</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -837,19 +837,19 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>70 m² tot.1 amb.1 dorm.1 baño1 coch.</t>
+          <t>70 m² tot.2 amb.1 dorm.1 baño1 coch.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa--zona-universitaria-recoleta-departamento-amoblado-58706430.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-departamento-2-ambientes-disponible-caballito.-58877206.html</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Recoleta, Capital Federal</t>
+          <t>Botánico, Palermo</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -859,100 +859,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>75 m² tot.2 amb.1 dorm.1 baño1 coch.</t>
+          <t>50 m² tot.2 amb.1 dorm.1 baño1 coch.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-hermoso-dos-ambientes-58714945.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Parque Chacabuco, Capital Federal</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>USD 750</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>45 m² tot.2 amb.1 dorm.1 baño</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-alquiler-loft-complejo-full-amenities-en-parque-58714790.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Recoleta, Capital Federal</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>$ 600.000</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>75 m² tot.2 amb.1 dorm.2 baños1 coch.</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-dos-ambientes-duenos-directo-58714927.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Caballito Norte, Caballito</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>$ 550.000</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>32 m² tot.1 amb.1 baño</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-dueno-alquila.-av-acoyte-y-aranguren-excelente-58714841.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Recoleta, Capital Federal</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>$ 600.000</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>75 m² tot.2 amb.1 dorm.1 baño</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-dos-ambientes-duenos-directo-58714878.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-departamento-2-premium-en-palermo-jardin-botanico.-58877204.html</t>
         </is>
       </c>
     </row>

--- a/Reporte_Oportunidades_InmoData.xlsx
+++ b/Reporte_Oportunidades_InmoData.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,418 +453,572 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Palermo, Capital Federal</t>
+          <t>Palermo Hollywood, Palermo</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>$ 600.000</t>
+          <t>USD 1.100</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>75 m² tot.2 amb.1 dorm.1 baño1 coch.</t>
+          <t>64 m² tot.2 amb.1 dorm.1 baño1 coch.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-hermoso-dos-ambientes-58879080.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-dueno-directo-duplex-en-alquiler-palermo-hollywood-53534920.html</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Recoleta, Capital Federal</t>
+          <t>Palermo Hollywood, Palermo</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>$ 750.000</t>
+          <t>$ 600.000</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>80 m² tot.3 amb.2 dorm.2 baños1 coch.</t>
+          <t>50 m² tot.2 amb.1 dorm.1 baño1 coch.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-depa-lujo-recoleta-58879176.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-palermo-alquiler-amoblado-dos-ambientes-frente-59016055.html</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Villa Pueyrredón, Capital Federal</t>
+          <t>Recoleta, Capital Federal</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>$ 660.000</t>
+          <t>$ 449.000</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>32 m² tot.1 amb.1 dorm.1 baño</t>
+          <t>23 m² tot.1 amb.1 baño</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-hermoso-monoambiente-de-categoria-en-villa-pueyrredon-58878546.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-alquilet-de-mono-ambiente-58432627.html</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Balvanera, Capital Federal</t>
+          <t>Belgrano R, Belgrano</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>$ 600.000</t>
+          <t>$ 550.000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>48 m² tot.2 amb.1 dorm.1 baño</t>
+          <t>75 m² tot.2 amb.1 dorm.1 baño1 coch.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-departamento-independencia-2105-58877999.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-dos-ambientes-59015930.html</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Villa Urquiza, Capital Federal</t>
+          <t>Palermo, Capital Federal</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>$ 600.000</t>
+          <t>$ 670.000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>39 m² tot.1 amb.</t>
+          <t>75 m² tot.3 amb.2 dorm.2 baños1 coch.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-monoambiente-en-alquiler-en-villa-urquiza!-58877922.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-departamento-3-ambientes-59015957.html</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Las Cañitas, Palermo</t>
+          <t>Palermo Hollywood, Palermo</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>USD 650</t>
+          <t>$ 600.000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>38 m² tot.</t>
+          <t>50 m² tot.2 amb.1 dorm.1 coch.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-jorge-newbery-1764-y-arce-58874045.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-palermo-alquiler-amoblado-2-ambientes-frente-balcon-59015931.html</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Botánico, Palermo</t>
+          <t>Monserrat, Capital Federal</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>$ 600.000</t>
+          <t>$ 980.000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>32 m² tot.1 amb.1 dorm.1 baño</t>
+          <t>95 m² tot.3 amb.2 dorm.1 baño</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-alquiler-dueno-directo-en-palermo-58877849.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-amplio-y-luminoso-departamento-al-frente-con-balcon-58197361.html</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Las Cañitas, Palermo</t>
+          <t>Palermo, Capital Federal</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>USD 650</t>
+          <t>$ 600.000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>35 m² tot.1 amb.1 dorm.1 baño</t>
+          <t>50 m² tot.2 amb.1 dorm.1 baño1 coch.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-alquiler-monoambiente-amoblado-58877525.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-palermo-alquiler-amoblado-2-ambientes-disponible-59015873.html</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Villa Crespo, Capital Federal</t>
+          <t>Recoleta, Capital Federal</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>$ 850.000</t>
+          <t>USD 2.950</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>47 m² tot.2 amb.1 dorm.1 baño</t>
+          <t>145 m² tot.4 amb.3 dorm.2 baños</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-departamento-2-ambientes-en-villa-crespo-58674105.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-3-dorm.-recoleta-listo-para-entrar-categoria-59015261.html</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Retiro, Capital Federal</t>
+          <t>Caballito, Capital Federal</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>$ 1.400.000</t>
+          <t>$ 600.000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>105 m² tot.4 amb.2 dorm.1 baño</t>
+          <t>50 m² tot.2 amb.1 dorm.1 baño1 coch.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-excelente-semipiso-en-recoleta-retiro-58734824.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-alquiler-de-dos-ambientes-ubicado-zona-caballito-59015818.html</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Recoleta, Capital Federal</t>
+          <t>Palermo Hollywood, Palermo</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>$ 1.050.000</t>
+          <t>$ 650.000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>53 m² tot.3 amb.2 dorm.1 baño</t>
+          <t>50 m² tot.2 amb.1 dorm.1 baño1 coch.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-palermo-3-amb-luminoso-alquiler-bajas-exp-58877539.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-palermo-alquiler-amoblado-de-dos-ambientes-frente-59015747.html</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Belgrano Chico, Belgrano</t>
+          <t>Monserrat, Capital Federal</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>$ 1.000.000</t>
+          <t>$ 750.000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>64 m² tot.1 amb.1 baño</t>
+          <t>46 m² tot.2 amb.1 dorm.1 baño</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-amplio-departamento-frente-a-av-libertador-58877431.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-departamento-penthouse-de-2-ambientes-muy-luminoso-y-59015745.html</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Recoleta, Capital Federal</t>
+          <t>Lomas de Núñez, Núñez</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>$ 1.200.000</t>
+          <t>$ 650.000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>57 m² tot.3 amb.2 dorm.1 baño1 coch.</t>
+          <t>35 m² tot.1 amb.1 baño</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-dueno-alquila-3ambientes-vista-abierta-cochera-58877323.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-hermoso-monoambiente-en-l-59015558.html</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Villa Urquiza, Capital Federal</t>
+          <t>Almagro Norte, Almagro</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>$ 830.000</t>
+          <t>$ 620.000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>64 m² tot.2 amb.1 dorm.1 baño1 coch.</t>
+          <t>55 m² tot.2 amb.1 dorm.1 baño</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-hermoso-duplex-2-amb.-cochera-cub-opcional.-en-la-53446991.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-hermoso-2-ambientes-super-luminoso-59015575.html</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Floresta Norte, Floresta</t>
+          <t>Recoleta, Capital Federal</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>$ 650.000</t>
+          <t>$ 500.000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>63 m² tot.3 amb.2 dorm.1 baño</t>
+          <t>20 m² tot.1 amb.1 dorm.1 baño</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-departamento-contrafrente-en-planta-baja-58874073.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-alquiler-monoambiente-rod-pena-1500-59015691.html</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Villa Urquiza, Capital Federal</t>
+          <t>Almagro Sur, Almagro</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>$ 650.000</t>
+          <t>$ 900.000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>41 m² tot.1 amb.1 baño</t>
+          <t>60 m² tot.4 amb.3 dorm.1 baño</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-hermoso-monoambiente-en-la-zona-mas-estrategica-de-58871227.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-hermoso-y-funcional-4-amb-en-alquiler-dueno-directo-59013966.html</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Palermo Nuevo, Palermo</t>
+          <t>Villa Crespo, Capital Federal</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>$ 500.000</t>
+          <t>$ 1.450.000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>25 m² tot.1 amb.1 baño</t>
+          <t>85 m² tot.4 amb.2 dorm.1 baño</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-alquiler-dueno-monoamb-pb-palermo-nuevo-frente-le-parc-58265665.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-departamento-de-3-ambientes-en-villa-crespo-con-jardin-59014697.html</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Caballito, Capital Federal</t>
+          <t>Barracas, Capital Federal</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>$ 550.000</t>
+          <t>USD 1.400</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>70 m² tot.2 amb.1 dorm.1 baño1 coch.</t>
+          <t>130 m² tot.1 amb.1 dorm.1 baño</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-departamento-2-ambientes-disponible-caballito.-58877206.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-exclusivo-loft-amoblado-edificio-historico-molina-59015348.html</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Botánico, Palermo</t>
+          <t>Recoleta, Capital Federal</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>$ 600.000</t>
+          <t>$ 500</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
+          <t>65 m² tot.2 amb.2 dorm.1 baño</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-alquileres-59015436.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Balvanera, Capital Federal</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>$ 900.000</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>42 m² tot.2 amb.1 dorm.1 baño</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-dueno-directo-alquila-57467613.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Recoleta, Capital Federal</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>$ 680.000</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>98 m² tot.2 amb.2 dorm.1 baño1 coch.</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-departamento-delia-59014982.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Palermo, Capital Federal</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>$ 650.000</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
           <t>50 m² tot.2 amb.1 dorm.1 baño1 coch.</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-departamento-2-premium-en-palermo-jardin-botanico.-58877204.html</t>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-departamento-de-2-ambientes-disponible-zona-palermo-59015015.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Caballito Sur, Caballito</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>$ 620.000</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>35 m² tot.1 amb.1 baño</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-monoambiente-amplio-apto-prof-dueno-directo-59014866.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Barrio Norte, Capital Federal</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>$ 1.100.000</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>74 m² tot.4 amb.3 dorm.2 baños</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-dueno-directo-alquila-depto-en-barrio-norte-caba-av-58950544.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Caballito, Capital Federal</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>$ 500</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>65 m² tot.2 amb.2 dorm.1 baño</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-alquileres-59014990.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>San Nicolás, Capital Federal</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>$ 900.000</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>70 m² tot.2 amb.1 dorm.1 baño</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-oportunidad-unica-ultimo-piso-terraza-privada-59014251.html</t>
         </is>
       </c>
     </row>

--- a/Reporte_Oportunidades_InmoData.xlsx
+++ b/Reporte_Oportunidades_InmoData.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,22 +453,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Palermo Hollywood, Palermo</t>
+          <t>Núñez, Capital Federal</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>USD 1.100</t>
+          <t>$ 750.000</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>64 m² tot.2 amb.1 dorm.1 baño1 coch.</t>
+          <t>36 m² tot.1 amb.1 dorm.1 baño</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-dueno-directo-duplex-en-alquiler-palermo-hollywood-53534920.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-dueno-directo-belgrano-nunez-monoambiente-amplio-54157665.html</t>
         </is>
       </c>
     </row>
@@ -480,17 +480,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>$ 600.000</t>
+          <t>USD 1.300</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>50 m² tot.2 amb.1 dorm.1 baño1 coch.</t>
+          <t>67 m² tot.2 amb.1 dorm.1 baño1 coch.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-palermo-alquiler-amoblado-dos-ambientes-frente-59016055.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-alquiler-de-2-ambientes-torres-palermo-view-piso-20-59161431.html</t>
         </is>
       </c>
     </row>
@@ -502,17 +502,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>$ 449.000</t>
+          <t>$ 550.000</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>23 m² tot.1 amb.1 baño</t>
+          <t>30 m² tot.1 amb.1 baño</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-alquilet-de-mono-ambiente-58432627.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-monoambiente-moderno.-alquiler-temporal.-ideal-para-58420093.html</t>
         </is>
       </c>
     </row>
@@ -524,90 +524,90 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>$ 550.000</t>
+          <t>USD 1.300</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>75 m² tot.2 amb.1 dorm.1 baño1 coch.</t>
+          <t>75 m² tot.3 amb.2 dorm.2 baños</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-dos-ambientes-59015930.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-departamento-luminoso-3-ambientes-belgrano-r-59445692.html</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Palermo, Capital Federal</t>
+          <t>Almagro Norte, Almagro</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>$ 670.000</t>
+          <t>$ 480.000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>75 m² tot.3 amb.2 dorm.2 baños1 coch.</t>
+          <t>33 m² tot.2 amb.1 dorm.1 baño</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-departamento-3-ambientes-59015957.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-dueno-alquila-departamento-de-2-ambientes-en-almagro-59445710.html</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Palermo Hollywood, Palermo</t>
+          <t>Boedo, Capital Federal</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>$ 600.000</t>
+          <t>USD 350</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>50 m² tot.2 amb.1 dorm.1 coch.</t>
+          <t>37 m² tot.1 baño</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-palermo-alquiler-amoblado-2-ambientes-frente-balcon-59015931.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-monoambiente-luminoso-59445685.html</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Monserrat, Capital Federal</t>
+          <t>Palermo Chico, Palermo</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>$ 980.000</t>
+          <t>$ 700.000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>95 m² tot.3 amb.2 dorm.1 baño</t>
+          <t>87 m² tot.2 amb.2 dorm.1 baño1 coch.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-amplio-y-luminoso-departamento-al-frente-con-balcon-58197361.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-departamento-en-alquiler-disponible.-59445671.html</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Palermo, Capital Federal</t>
+          <t>Almagro, Capital Federal</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -617,232 +617,232 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>50 m² tot.2 amb.1 dorm.1 baño1 coch.</t>
+          <t>1 m² tot.1 amb.1 baño1 coch.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-palermo-alquiler-amoblado-2-ambientes-disponible-59015873.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-impecable-monoambiente-con-balcon-y-cochera-en-59445596.html</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Recoleta, Capital Federal</t>
+          <t>Flores Norte, Flores</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>USD 2.950</t>
+          <t>$ 799.900</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>145 m² tot.4 amb.3 dorm.2 baños</t>
+          <t>48 m² tot.2 amb.1 dorm.1 baño</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-3-dorm.-recoleta-listo-para-entrar-categoria-59015261.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-2-ambientes-reciclado-a-nuevo-con-balcon-al-frente-59445503.html</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Caballito, Capital Federal</t>
+          <t>Belgrano C, Belgrano</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>$ 600.000</t>
+          <t>$ 1.200.000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>50 m² tot.2 amb.1 dorm.1 baño1 coch.</t>
+          <t>58 m² tot.2 amb.1 dorm.1 baño</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-alquiler-de-dos-ambientes-ubicado-zona-caballito-59015818.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-alquiler-belgrano-a-estrenar-59445072.html</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Palermo Hollywood, Palermo</t>
+          <t>Belgrano C, Belgrano</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>$ 650.000</t>
+          <t>$ 850.000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>50 m² tot.2 amb.1 dorm.1 baño1 coch.</t>
+          <t>44 m² tot.1 amb.1 baño</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-palermo-alquiler-amoblado-de-dos-ambientes-frente-59015747.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-excelente-depto.-1-amb-en-belgrano-super-luminoso-y-59432773.html</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Monserrat, Capital Federal</t>
+          <t>Retiro, Capital Federal</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>$ 750.000</t>
+          <t>USD 1.200</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>46 m² tot.2 amb.1 dorm.1 baño</t>
+          <t>55 m² tot.3 amb.2 dorm.1 baño</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-departamento-penthouse-de-2-ambientes-muy-luminoso-y-59015745.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-alquiler-departamento-3-ambientes-dueno-directo-59444889.html</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Lomas de Núñez, Núñez</t>
+          <t>Belgrano, Capital Federal</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>$ 650.000</t>
+          <t>$ 1.800.000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>35 m² tot.1 amb.1 baño</t>
+          <t>86 m² tot.4 amb.3 dorm.2 baños1 coch.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-hermoso-monoambiente-en-l-59015558.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-semipiso-de-4-amb-frente-balcon-cochera.-piscina-54276180.html</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Almagro Norte, Almagro</t>
+          <t>Belgrano, Capital Federal</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>$ 620.000</t>
+          <t>$ 650.000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>55 m² tot.2 amb.1 dorm.1 baño</t>
+          <t>41 m² tot.2 amb.1 dorm.1 baño</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-hermoso-2-ambientes-super-luminoso-59015575.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-departamento-2-ambientes-contrafrente-en-belgrano.-59444009.html</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Recoleta, Capital Federal</t>
+          <t>Villa Ortuzar, Capital Federal</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>$ 500.000</t>
+          <t>$ 615.000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>20 m² tot.1 amb.1 dorm.1 baño</t>
+          <t>40 m² tot.2 amb.1 dorm.1 baño</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-alquiler-monoambiente-rod-pena-1500-59015691.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-2-ambientes-luminoso-en-villa-ortuzar-cerca-subte-b-59444037.html</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Almagro Sur, Almagro</t>
+          <t>Lomas de Núñez, Núñez</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>$ 900.000</t>
+          <t>$ 725.000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>60 m² tot.4 amb.3 dorm.1 baño</t>
+          <t>36 m² tot.1 amb.1 baño</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-hermoso-y-funcional-4-amb-en-alquiler-dueno-directo-59013966.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-monoambiente-a-estrenar-en-el-barrio-de-nunez-dueno-59443682.html</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Villa Crespo, Capital Federal</t>
+          <t>Recoleta, Capital Federal</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>$ 1.450.000</t>
+          <t>$ 1.650.000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>85 m² tot.4 amb.2 dorm.1 baño</t>
+          <t>88 m² tot.2 dorm.2 baños</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-departamento-de-3-ambientes-en-villa-crespo-con-jardin-59014697.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-semipiso-contrafrente-56499422.html</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Barracas, Capital Federal</t>
+          <t>San Nicolás, Capital Federal</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>USD 1.400</t>
+          <t>$ 1.200.000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>130 m² tot.1 amb.1 dorm.1 baño</t>
+          <t>79 m² tot.3 amb.2 dorm.1 baño</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-exclusivo-loft-amoblado-edificio-historico-molina-59015348.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-semipiso-de-categoria:-estilo-clasico-y-confort-59443145.html</t>
         </is>
       </c>
     </row>
@@ -854,171 +854,259 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>$ 500</t>
+          <t>$ 1.000.000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>65 m² tot.2 amb.2 dorm.1 baño</t>
+          <t>68 m² tot.2 amb.1 dorm.2 baños</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-alquileres-59015436.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-dueno-alquila-2-ambientes-a-estrenar-59443365.html</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Balvanera, Capital Federal</t>
+          <t>Recoleta, Capital Federal</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>$ 900.000</t>
+          <t>$ 550</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>42 m² tot.2 amb.1 dorm.1 baño</t>
+          <t>41 m² tot.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-dueno-directo-alquila-57467613.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-departamento-en-alquiler-ubicado-en-recoleta-59443426.html</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Recoleta, Capital Federal</t>
+          <t>Parque Chas, Capital Federal</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>$ 680.000</t>
+          <t>USD 1.100</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>98 m² tot.2 amb.2 dorm.1 baño1 coch.</t>
+          <t>80 m² tot.3 amb.2 baños</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-departamento-delia-59014982.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-av-de-los-incas-5066-59443328.html</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Palermo, Capital Federal</t>
+          <t>Recoleta, Capital Federal</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>$ 650.000</t>
+          <t>$ 1.899.999</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>50 m² tot.2 amb.1 dorm.1 baño1 coch.</t>
+          <t>54 m² tot.2 amb.1 dorm.2 baños</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-departamento-de-2-ambientes-disponible-zona-palermo-59015015.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-alto-palermo.-2-amb.-2-banos.-opt.-1-coch-cubierta.-53465289.html</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Caballito Sur, Caballito</t>
+          <t>Recoleta, Capital Federal</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>$ 620.000</t>
+          <t>$ 1.400.000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>35 m² tot.1 amb.1 baño</t>
+          <t>55 m² tot.3 amb.2 dorm.1 baño</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-monoambiente-amplio-apto-prof-dueno-directo-59014866.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-dueno-directo-impecable-3-ambientes-reciclado-en-59443273.html</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Barrio Norte, Capital Federal</t>
+          <t>Caballito Sur, Caballito</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>$ 1.100.000</t>
+          <t>$ 520.000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>74 m² tot.4 amb.3 dorm.2 baños</t>
+          <t>27 m² tot.1 amb.1 baño</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-dueno-directo-alquila-depto-en-barrio-norte-caba-av-58950544.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-monoambiente-con-balcon-en-caballito-apto-profesional-53473554.html</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Caballito, Capital Federal</t>
+          <t>Recoleta, Capital Federal</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>$ 500</t>
+          <t>$ 1.300.000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>65 m² tot.2 amb.2 dorm.1 baño</t>
+          <t>62 m² tot.3 amb.2 dorm.1 baño</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-alquileres-59014990.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-alquilo-recoleta-3-ambientes-bano-toilette-terraza-y-59442218.html</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>San Nicolás, Capital Federal</t>
+          <t>Palermo Chico, Palermo</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>$ 900.000</t>
+          <t>$ 1.490.000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>70 m² tot.2 amb.1 dorm.1 baño</t>
+          <t>83 m² tot.3 amb.3 dorm.1 baño</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-oportunidad-unica-ultimo-piso-terraza-privada-59014251.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-dueno-directo-alquila-departamento-semipiso-palermo-53550985.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Monserrat, Capital Federal</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>$ 1.100.000</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>75 m² tot.4 amb.2 dorm.1 baño</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-excelente-4-ambientes.-todo-luz.-dueno-directo.-55281756.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Recoleta, Capital Federal</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>$ 850.000</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>48 m² tot.2 amb.1 dorm.1 baño</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-edificio-premium-seg-24-hs-depto-dos-ambientes-59379241.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Palermo, Capital Federal</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>$ 849.999</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>54 m² tot.1 amb.1 dorm.1 baño1 coch.</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-botanico-palermo-studio-tipo-loft.-cocina-y-bano-53734134.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Botánico, Palermo</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>USD 1.600</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>140 m² tot.2 amb.2 dorm.1 baño</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-vista-panoramica-59442184.html</t>
         </is>
       </c>
     </row>

--- a/Reporte_Oportunidades_InmoData.xlsx
+++ b/Reporte_Oportunidades_InmoData.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,22 +417,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Barrio</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Precio</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Descripcion</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Link</t>
         </is>
@@ -453,396 +441,396 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Núñez, Capital Federal</t>
+          <t>San Cristobal, Capital Federal</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>$ 750.000</t>
+          <t>$ 700.000</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>36 m² tot.1 amb.1 dorm.1 baño</t>
+          <t>44 m² tot.2 amb.1 dorm.1 baño</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-dueno-directo-belgrano-nunez-monoambiente-amplio-54157665.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-alquiler-departamento-a-estrenar-de-categoria-en-san-59648270.html</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Palermo Hollywood, Palermo</t>
+          <t>Villa Urquiza, Capital Federal</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>USD 1.300</t>
+          <t>$ 700.000</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>67 m² tot.2 amb.1 dorm.1 baño1 coch.</t>
+          <t>47 m² tot.2 amb.1 dorm.1 baño1 coch.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-alquiler-de-2-ambientes-torres-palermo-view-piso-20-59161431.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-villa-urquiza-ingreso-inmediato-dos-ambientes-59648255.html</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Recoleta, Capital Federal</t>
+          <t>Palermo Soho, Palermo</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>$ 550.000</t>
+          <t>$ 1.500.000</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>30 m² tot.1 amb.1 baño</t>
+          <t>63 m² tot.3 amb.2 dorm.1 baño1 coch.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-monoambiente-moderno.-alquiler-temporal.-ideal-para-58420093.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-semipiso-con-palier-semiprivado-con-cochera-59648146.html</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Belgrano R, Belgrano</t>
+          <t>La Boca, Capital Federal</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>USD 1.300</t>
+          <t>$ 600.000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>75 m² tot.3 amb.2 dorm.2 baños</t>
+          <t>50 m² tot.2 amb.1 dorm.1 baño</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-departamento-luminoso-3-ambientes-belgrano-r-59445692.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-departamento-2-ambientes-en-la-boca-frente-a-hospital-59648133.html</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Almagro Norte, Almagro</t>
+          <t>Núñez, Capital Federal</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>$ 480.000</t>
+          <t>USD 1.200</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>33 m² tot.2 amb.1 dorm.1 baño</t>
+          <t>85 m² tot.4 amb.2 dorm.2 baños1 coch.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-dueno-alquila-departamento-de-2-ambientes-en-almagro-59445710.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-hermoso-duplex-con-cochera-y-amenitis!-59648092.html</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Boedo, Capital Federal</t>
+          <t>San Nicolás, Capital Federal</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>USD 350</t>
+          <t>$ 800.000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>37 m² tot.1 baño</t>
+          <t>49 m² tot.3 amb.2 dorm.1 baño</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-monoambiente-luminoso-59445685.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-alquilo-3-4-amb-zona-obelisco-corrientes-y-libertad-59619240.html</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Palermo Chico, Palermo</t>
+          <t>Belgrano R, Belgrano</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>$ 700.000</t>
+          <t>$ 1.500.000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>87 m² tot.2 amb.2 dorm.1 baño1 coch.</t>
+          <t>42 m² tot.2 amb.1 dorm.1 baño</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-departamento-en-alquiler-disponible.-59445671.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-departamento-alquiler-2-ambientes-amoblado-belgrano-59647977.html</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Almagro, Capital Federal</t>
+          <t>Recoleta, Capital Federal</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>$ 600.000</t>
+          <t>$ 690.000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1 m² tot.1 amb.1 baño1 coch.</t>
+          <t>75 m² tot.3 amb.2 dorm.2 baños1 coch.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-impecable-monoambiente-con-balcon-y-cochera-en-59445596.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-departamento-3-ambientes-en-recoleta-59647894.html</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Flores Norte, Flores</t>
+          <t>Villa Crespo, Capital Federal</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>$ 799.900</t>
+          <t>$ 670.000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>48 m² tot.2 amb.1 dorm.1 baño</t>
+          <t>42 m² tot.1 amb.1 baño</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-2-ambientes-reciclado-a-nuevo-con-balcon-al-frente-59445503.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-monoambiente-en-villa-crespo-palermo-53211995.html</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Belgrano C, Belgrano</t>
+          <t>Villa Crespo, Capital Federal</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>$ 1.200.000</t>
+          <t>$ 875.000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>58 m² tot.2 amb.1 dorm.1 baño</t>
+          <t>47 m² tot.2 amb.1 dorm.1 baño</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-alquiler-belgrano-a-estrenar-59445072.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-hermoso-departamento-2-ambientes-al-contrafrente-muy-59647571.html</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Belgrano C, Belgrano</t>
+          <t>La Paternal, Capital Federal</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>$ 850.000</t>
+          <t>$ 780.000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>44 m² tot.1 amb.1 baño</t>
+          <t>50 m² tot.2 amb.1 dorm.2 baños</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-excelente-depto.-1-amb-en-belgrano-super-luminoso-y-59432773.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-hermoso-departamento-dos-ambientes-c-dos-banos-y-59501650.html</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Retiro, Capital Federal</t>
+          <t>Recoleta, Capital Federal</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>USD 1.200</t>
+          <t>USD 2.200</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>55 m² tot.3 amb.2 dorm.1 baño</t>
+          <t>140 m² tot.4 amb.2 dorm.3 baños1 coch.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-alquiler-departamento-3-ambientes-dueno-directo-59444889.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-exclusivo-duplex-de-4-ambientes-con-cochera-terrazas-59647264.html</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Belgrano, Capital Federal</t>
+          <t>Núñez, Capital Federal</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>$ 1.800.000</t>
+          <t>$ 680.000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>86 m² tot.4 amb.3 dorm.2 baños1 coch.</t>
+          <t>65 m² tot.3 amb.2 dorm.2 baños1 coch.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-semipiso-de-4-amb-frente-balcon-cochera.-piscina-54276180.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-hermoso-departamento-3-ambientes-ubicado-en-nunes-59645175.html</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Belgrano, Capital Federal</t>
+          <t>Primera Junta, Caballito</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>$ 650.000</t>
+          <t>$ 680.000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>41 m² tot.2 amb.1 dorm.1 baño</t>
+          <t>60 m² tot.2 amb.1 dorm.1 baño</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-departamento-2-ambientes-contrafrente-en-belgrano.-59444009.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-excelente-oportunidad-ubicacion-inmejorable-piso-59381571.html</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Villa Ortuzar, Capital Federal</t>
+          <t>Palermo, Capital Federal</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>$ 615.000</t>
+          <t>$ 700.000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>40 m² tot.2 amb.1 dorm.1 baño</t>
+          <t>43 m² tot.2 amb.1 dorm.1 baño</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-2-ambientes-luminoso-en-villa-ortuzar-cerca-subte-b-59444037.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-amplio-2-amb.-en-palermo-excelente-ubicacion-a-m-del-58822356.html</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Lomas de Núñez, Núñez</t>
+          <t>Recoleta, Capital Federal</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>$ 725.000</t>
+          <t>$ 620.000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>36 m² tot.1 amb.1 baño</t>
+          <t>29 m² tot.1 amb.1 baño</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-monoambiente-a-estrenar-en-el-barrio-de-nunez-dueno-59443682.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-monoambiente-cocina-separada.-29-m-sup2-59643789.html</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Recoleta, Capital Federal</t>
+          <t>Villa General Mitre, Capital Federal</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>$ 1.650.000</t>
+          <t>$ 1.250.000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>88 m² tot.2 dorm.2 baños</t>
+          <t>95 m² tot.4 amb.3 dorm.2 baños</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-semipiso-contrafrente-56499422.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-impecable-4-ambientes-al-frente-sobre-magarinos-59643661.html</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>San Nicolás, Capital Federal</t>
+          <t>Recoleta, Capital Federal</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>$ 1.200.000</t>
+          <t>$ 900.000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>79 m² tot.3 amb.2 dorm.1 baño</t>
+          <t>45 m² tot.2 amb.1 dorm.1 baño</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-semipiso-de-categoria:-estilo-clasico-y-confort-59443145.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-alquiler-departamento-2-ambientes-mas-baulera-59605199.html</t>
         </is>
       </c>
     </row>
@@ -854,193 +842,193 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>$ 1.000.000</t>
+          <t>USD 500</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>68 m² tot.2 amb.1 dorm.2 baños</t>
+          <t>30 m² tot.1 amb.1 dorm.1 baño</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-dueno-alquila-2-ambientes-a-estrenar-59443365.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-monoambiente-equipado-56536654.html</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Recoleta, Capital Federal</t>
+          <t>Lomas de Núñez, Núñez</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>$ 550</t>
+          <t>USD 750</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>41 m² tot.</t>
+          <t>42 m² tot.2 amb.1 dorm.1 baño</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-departamento-en-alquiler-ubicado-en-recoleta-59443426.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-alquiler-tradicional-amoblado-nunez-59642278.html</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Parque Chas, Capital Federal</t>
+          <t>Villa Urquiza, Capital Federal</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>USD 1.100</t>
+          <t>$ 650.000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>80 m² tot.3 amb.2 baños</t>
+          <t>38 m² tot.1 amb.1 dorm.1 baño</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-av-de-los-incas-5066-59443328.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-alquiler-en-villa-urquiza-monoambiente-con-balcon-59636196.html</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Recoleta, Capital Federal</t>
+          <t>Balvanera, Capital Federal</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>$ 1.899.999</t>
+          <t>$ 800.000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>54 m² tot.2 amb.1 dorm.2 baños</t>
+          <t>32 m² tot.1 amb.1 baño</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-alto-palermo.-2-amb.-2-banos.-opt.-1-coch-cubierta.-53465289.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-comodo-monoambiente-se-puede-hacer-divisible-sin-59643404.html</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Recoleta, Capital Federal</t>
+          <t>Villa Urquiza, Capital Federal</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>$ 1.400.000</t>
+          <t>$ 1.350.000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>55 m² tot.3 amb.2 dorm.1 baño</t>
+          <t>60 m² tot.3 amb.2 dorm.1 baño</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-dueno-directo-impecable-3-ambientes-reciclado-en-59443273.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-alquiler-3-ambientes-con-baulera-semi-piso-al-frente-59643265.html</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Caballito Sur, Caballito</t>
+          <t>Almagro Norte, Almagro</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>$ 520.000</t>
+          <t>USD 650</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>27 m² tot.1 amb.1 baño</t>
+          <t>51 m² tot.2 amb.1 dorm.1 baño</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-monoambiente-con-balcon-en-caballito-apto-profesional-53473554.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-almagro-2-ambientes-amoblado-con-balcon-y-bajas-59285286.html</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Recoleta, Capital Federal</t>
+          <t>Palermo Hollywood, Palermo</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>$ 1.300.000</t>
+          <t>$ 1.000.000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>62 m² tot.3 amb.2 dorm.1 baño</t>
+          <t>60 m² tot.3 amb.2 dorm.1 baño1 coch.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-alquilo-recoleta-3-ambientes-bano-toilette-terraza-y-59442218.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-departamento-tres-ambientes-palermo-hollywood-caba-59643017.html</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Palermo Chico, Palermo</t>
+          <t>Villa Crespo, Capital Federal</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>$ 1.490.000</t>
+          <t>$ 600.000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>83 m² tot.3 amb.3 dorm.1 baño</t>
+          <t>30 m² tot.1 amb.1 baño</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-dueno-directo-alquila-departamento-semipiso-palermo-53550985.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-excelente-monoambiente-59642443.html</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Monserrat, Capital Federal</t>
+          <t>Palermo Hollywood, Palermo</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>$ 1.100.000</t>
+          <t>$ 650.000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>75 m² tot.4 amb.2 dorm.1 baño</t>
+          <t>35 m² tot.1 amb.1 dorm.1 baño</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-excelente-4-ambientes.-todo-luz.-dueno-directo.-55281756.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-un-ambiente-y-medio-dividido-impecable-24-meses-sin-59642664.html</t>
         </is>
       </c>
     </row>
@@ -1052,61 +1040,61 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>$ 850.000</t>
+          <t>$ 1.600.000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>48 m² tot.2 amb.1 dorm.1 baño</t>
+          <t>75 m² tot.4 amb.3 dorm.1 baño1 coch.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-edificio-premium-seg-24-hs-depto-dos-ambientes-59379241.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-dueno-directo.-todo-luz.-excelente-ubicacion-recoleta-58361895.html</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Palermo, Capital Federal</t>
+          <t>Chacarita, Capital Federal</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>$ 849.999</t>
+          <t>$ 550.000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>54 m² tot.1 amb.1 dorm.1 baño1 coch.</t>
+          <t>36 m² tot.2 amb.1 dorm.1 baño</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-botanico-palermo-studio-tipo-loft.-cocina-y-bano-53734134.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-dueno-alquila-dpto-2-av-corrientes-y-dorrego-lateral-57241867.html</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Botánico, Palermo</t>
+          <t>Recoleta, Capital Federal</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>USD 1.600</t>
+          <t>$ 500.000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>140 m² tot.2 amb.2 dorm.1 baño</t>
+          <t>29 m² tot.2 amb.1 dorm.1 baño</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-vista-panoramica-59442184.html</t>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-dueno-alquila-dpto-2-ambientes-lateral-super-luminoso-57250660.html</t>
         </is>
       </c>
     </row>

--- a/Reporte_Oportunidades_InmoData.xlsx
+++ b/Reporte_Oportunidades_InmoData.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,26 +425,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Zona</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Barrio</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Precio</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Descripcion</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Link</t>
         </is>
@@ -441,660 +458,999 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>San Cristobal, Capital Federal</t>
+          <t>Capital Federal</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>$ 700.000</t>
+          <t>Villa del Parque, Capital Federal</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>44 m² tot.2 amb.1 dorm.1 baño</t>
+          <t>$ 600.000</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-alquiler-departamento-a-estrenar-de-categoria-en-san-59648270.html</t>
+          <t>42 m² tot.2 amb.1 dorm.1 baño</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-alquilo-2-ambientes-en-villa-del-parque-59230846.html</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Villa Urquiza, Capital Federal</t>
+          <t>Capital Federal</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>$ 700.000</t>
+          <t>Villa Pueyrredón, Capital Federal</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>47 m² tot.2 amb.1 dorm.1 baño1 coch.</t>
+          <t>$ 850.000</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-villa-urquiza-ingreso-inmediato-dos-ambientes-59648255.html</t>
+          <t>50 m² tot.2 amb.1 baño</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-dueno-directo-moderno-duplex-2-ambientes-loft-en-59746641.html</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Palermo Soho, Palermo</t>
+          <t>Capital Federal</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>$ 1.500.000</t>
+          <t>San Telmo, Capital Federal</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>63 m² tot.3 amb.2 dorm.1 baño1 coch.</t>
+          <t>$ 800.000</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-semipiso-con-palier-semiprivado-con-cochera-59648146.html</t>
+          <t>50 m² tot.3 amb.2 dorm.1 baño</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-departamento-amueblado-3-amb-san-telmo-59746897.html</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>La Boca, Capital Federal</t>
+          <t>Capital Federal</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>Monserrat, Capital Federal</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>$ 600.000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>50 m² tot.2 amb.1 dorm.1 baño</t>
-        </is>
-      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-departamento-2-ambientes-en-la-boca-frente-a-hospital-59648133.html</t>
+          <t>47 m² tot.2 amb.1 dorm.1 baño</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-departamento-de-2-ambientes-58929308.html</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Núñez, Capital Federal</t>
+          <t>Capital Federal</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>USD 1.200</t>
+          <t>Parque Rivadavia, Caballito</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>85 m² tot.4 amb.2 dorm.2 baños1 coch.</t>
+          <t>$ 1.500.000</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-hermoso-duplex-con-cochera-y-amenitis!-59648092.html</t>
+          <t>130 m² tot.4 amb.3 dorm.3 baños1 coch.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-dueno-directo-alquila-depto-en-caballito-59253326.html</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>San Nicolás, Capital Federal</t>
+          <t>Capital Federal</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>$ 800.000</t>
+          <t>Belgrano Chico, Belgrano</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>49 m² tot.3 amb.2 dorm.1 baño</t>
+          <t>$ 1.200.000</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-alquilo-3-4-amb-zona-obelisco-corrientes-y-libertad-59619240.html</t>
+          <t>42 m² tot.1 amb.1 baño1 coch.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-monoambiente-con-cochera-y-amenities-en-belgrano-chico-59745869.html</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Belgrano R, Belgrano</t>
+          <t>Capital Federal</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>$ 1.500.000</t>
+          <t>Villa Lugano, Capital Federal</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>42 m² tot.2 amb.1 dorm.1 baño</t>
+          <t>$ 680.000</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-departamento-alquiler-2-ambientes-amoblado-belgrano-59647977.html</t>
+          <t>50 m² tot.2 amb.1 dorm.1 baño</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-dueno-alquila-2-amb.-c-balcon-lugano-caba-59744904.html</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Recoleta, Capital Federal</t>
+          <t>Capital Federal</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>$ 690.000</t>
+          <t>Belgrano C, Belgrano</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>75 m² tot.3 amb.2 dorm.2 baños1 coch.</t>
+          <t>$ 1.500.000</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-departamento-3-ambientes-en-recoleta-59647894.html</t>
+          <t>59 m² tot.3 amb.2 dorm.1 baño1 coch.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-super-luminoso-confrafrente-abierto-con-cochera-59701697.html</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Villa Crespo, Capital Federal</t>
+          <t>Capital Federal</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>$ 670.000</t>
+          <t>Mataderos, Capital Federal</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>42 m² tot.1 amb.1 baño</t>
+          <t>$ 699.000</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-monoambiente-en-villa-crespo-palermo-53211995.html</t>
+          <t>37 m² tot.2 amb.1 dorm.1 baño</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-dueno-alq-2-ambientes-en-mataderos-c-excelentes-49400033.html</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Villa Crespo, Capital Federal</t>
+          <t>Capital Federal</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>$ 875.000</t>
+          <t>Villa Urquiza, Capital Federal</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>47 m² tot.2 amb.1 dorm.1 baño</t>
+          <t>USD 600</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-hermoso-departamento-2-ambientes-al-contrafrente-muy-59647571.html</t>
+          <t>41 m² tot.1 amb.1 dorm.1 baño</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-luminoso-monoambiente-amueblado-con-balcon-en-villa-58466256.html</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>La Paternal, Capital Federal</t>
+          <t>Capital Federal</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>$ 780.000</t>
+          <t>Monserrat, Capital Federal</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>50 m² tot.2 amb.1 dorm.2 baños</t>
+          <t>$ 500.000</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-hermoso-departamento-dos-ambientes-c-dos-banos-y-59501650.html</t>
+          <t>25 m² tot.1 amb.1 baño</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-luminoso-monoambiente-con-expensas-y-servicios-59744498.html</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Recoleta, Capital Federal</t>
+          <t>Capital Federal</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>USD 2.200</t>
+          <t>San Telmo, Capital Federal</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>140 m² tot.4 amb.2 dorm.3 baños1 coch.</t>
+          <t>USD 600</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-exclusivo-duplex-de-4-ambientes-con-cochera-terrazas-59647264.html</t>
+          <t>55 m² tot.3 amb.2 dorm.1 baño</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-hermoso-3amb-equipado-luminoso-en-mejor-zona-san-telmo-59744724.html</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Núñez, Capital Federal</t>
+          <t>Capital Federal</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>$ 680.000</t>
+          <t>Botánico, Palermo</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>65 m² tot.3 amb.2 dorm.2 baños1 coch.</t>
+          <t>$ 1.350.000</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-hermoso-departamento-3-ambientes-ubicado-en-nunes-59645175.html</t>
+          <t>120 m² tot.3 amb.2 dorm.1 baño</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-dueno-3-ambientes.-palermo.-gran-terraza-propia-de-50-59744694.html</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Primera Junta, Caballito</t>
+          <t>Capital Federal</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>$ 680.000</t>
+          <t>Parque Avellaneda, Capital Federal</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>60 m² tot.2 amb.1 dorm.1 baño</t>
+          <t>$ 800.000</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-excelente-oportunidad-ubicacion-inmejorable-piso-59381571.html</t>
+          <t>80 m² tot.3 amb.2 dorm.1 baño</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-due-o-alquila-sin-expensas-59744181.html</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Palermo, Capital Federal</t>
+          <t>Capital Federal</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>$ 700.000</t>
+          <t>Monserrat, Capital Federal</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>43 m² tot.2 amb.1 dorm.1 baño</t>
+          <t>USD 1.200</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-amplio-2-amb.-en-palermo-excelente-ubicacion-a-m-del-58822356.html</t>
+          <t>80 m² tot.4 amb.3 dorm.2 baños</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-alquiler-monserrat-departamento-80-m-sup2--4-59744265.html</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Recoleta, Capital Federal</t>
+          <t>Capital Federal</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>$ 620.000</t>
+          <t>Coghlan, Capital Federal</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>29 m² tot.1 amb.1 baño</t>
+          <t>$ 750.000</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-monoambiente-cocina-separada.-29-m-sup2-59643789.html</t>
+          <t>49 m² tot.2 amb.1 dorm.1 baño</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-dueno-alquila-2-ambientes-como-nuevo-al-frente-en-56648742.html</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Villa General Mitre, Capital Federal</t>
+          <t>Capital Federal</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>$ 1.250.000</t>
+          <t>Balvanera, Capital Federal</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>95 m² tot.4 amb.3 dorm.2 baños</t>
+          <t>USD 500</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-impecable-4-ambientes-al-frente-sobre-magarinos-59643661.html</t>
+          <t>75 m² tot.2 amb.1 dorm.1 baño</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-alquiler-2-ambientes-balvanera-59743994.html</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Recoleta, Capital Federal</t>
+          <t>Capital Federal</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>$ 900.000</t>
+          <t>Villa del Parque, Capital Federal</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>45 m² tot.2 amb.1 dorm.1 baño</t>
+          <t>$ 950.000</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-alquiler-departamento-2-ambientes-mas-baulera-59605199.html</t>
+          <t>100 m² tot.2 amb.1 dorm.1 baño</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-departamento-2-ambientes-con-balcon-terraza-grande-59740361.html</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Recoleta, Capital Federal</t>
+          <t>Capital Federal</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>USD 500</t>
+          <t>Las Cañitas, Palermo</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>30 m² tot.1 amb.1 dorm.1 baño</t>
+          <t>USD 1.700</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-monoambiente-equipado-56536654.html</t>
+          <t>74 m² tot.3 amb.2 dorm.1 baño1 coch.</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-dept-3-amb.-con-piscina-cochera-y-seguridad-las-51633093.html</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Lomas de Núñez, Núñez</t>
+          <t>Capital Federal</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>USD 750</t>
+          <t>Villa del Parque, Capital Federal</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>42 m² tot.2 amb.1 dorm.1 baño</t>
+          <t>$ 880.000</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-alquiler-tradicional-amoblado-nunez-59642278.html</t>
+          <t>70 m² tot.3 amb.2 dorm.1 baño</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-alquilo-departamento-3-ambientes-en-villa-del-parque-59739878.html</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Villa Urquiza, Capital Federal</t>
+          <t>Capital Federal</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>$ 650.000</t>
+          <t>Villa Crespo, Capital Federal</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>38 m² tot.1 amb.1 dorm.1 baño</t>
+          <t>$ 740.000</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-alquiler-en-villa-urquiza-monoambiente-con-balcon-59636196.html</t>
+          <t>40 m² tot.2 amb.1 dorm.1 baño</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-dos-ambientes-luminoso-amoblado.-parque-centenario.-56113938.html</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Balvanera, Capital Federal</t>
+          <t>Capital Federal</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>$ 800.000</t>
+          <t>Caballito Sur, Caballito</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>32 m² tot.1 amb.1 baño</t>
+          <t>$ 550.000</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-comodo-monoambiente-se-puede-hacer-divisible-sin-59643404.html</t>
+          <t>38 m² tot.2 amb.1 dorm.1 baño</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-alquiler-2-ambientes-con-balcon-caballito-59467287.html</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Villa Urquiza, Capital Federal</t>
+          <t>Capital Federal</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>$ 1.350.000</t>
+          <t>San Nicolás, Capital Federal</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>60 m² tot.3 amb.2 dorm.1 baño</t>
+          <t>$ 450.000</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-alquiler-3-ambientes-con-baulera-semi-piso-al-frente-59643265.html</t>
+          <t>24 m² tot.1 amb.1 baño</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-un-ambiente-al-frente-59743790.html</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Almagro Norte, Almagro</t>
+          <t>Capital Federal</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>USD 650</t>
+          <t>Palermo Hollywood, Palermo</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>51 m² tot.2 amb.1 dorm.1 baño</t>
+          <t>$ 890.000</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-almagro-2-ambientes-amoblado-con-balcon-y-bajas-59285286.html</t>
+          <t>45 m² tot.2 amb.1 dorm.1 baño</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-alquiler-departamento-en-palermo-dos-ambientes-2-59743717.html</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Palermo Hollywood, Palermo</t>
+          <t>Capital Federal</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>$ 1.000.000</t>
+          <t>Villa Devoto, Capital Federal</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>60 m² tot.3 amb.2 dorm.1 baño1 coch.</t>
+          <t>$ 700.000</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-departamento-tres-ambientes-palermo-hollywood-caba-59643017.html</t>
+          <t>36 m² tot.1 amb.1 baño</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-alquiler-4-piso-b-contrafrente-59743361.html</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Villa Crespo, Capital Federal</t>
+          <t>Capital Federal</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>$ 600.000</t>
+          <t>Concepción, Colegiales</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>30 m² tot.1 amb.1 baño</t>
+          <t>USD 600</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-excelente-monoambiente-59642443.html</t>
+          <t>44 m² tot.1 amb.1 dorm.1 baño</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-divino-monoambiente-equipado-para-2-personas-59742643.html</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Palermo Hollywood, Palermo</t>
+          <t>Capital Federal</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>$ 650.000</t>
+          <t>Villa Crespo, Capital Federal</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>35 m² tot.1 amb.1 dorm.1 baño</t>
+          <t>$ 820.000</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-un-ambiente-y-medio-dividido-impecable-24-meses-sin-59642664.html</t>
+          <t>35 m² tot.2 amb.1 dorm.1 baño</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-dos-ambientes-en-villa-crespo-bajisimas-expensas-dueno-59742834.html</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Recoleta, Capital Federal</t>
+          <t>Fuera de Capital</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>$ 1.600.000</t>
+          <t>Valle Escondido , Córdoba</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>75 m² tot.4 amb.3 dorm.1 baño1 coch.</t>
+          <t>$ 1.400.000</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-dueno-directo.-todo-luz.-excelente-ubicacion-recoleta-58361895.html</t>
+          <t>99 m² tot.3 amb.2 dorm.2 baños1 coch.</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclapin-departamento-en-valle-escondido-58697575.html</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Chacarita, Capital Federal</t>
+          <t>Fuera de Capital</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>$ 550.000</t>
+          <t>Palermo Hollywood, Palermo</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>36 m² tot.2 amb.1 dorm.1 baño</t>
+          <t>USD 2.200</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-dueno-alquila-dpto-2-av-corrientes-y-dorrego-lateral-57241867.html</t>
+          <t>84 m² tot.3 amb.2 dorm.2 baños1 coch.</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclapin-alquiler-3-ambientes-c-cochera-en-mirabilia-palermo-en-59548246.html</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Recoleta, Capital Federal</t>
+          <t>Fuera de Capital</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
+          <t>Quilmes, GBA Sur</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>$ 750.000</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>65 m² tot.2 amb.1 dorm.1 baño1 coch.</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclapin-departamento-en-alquiler-de-2-ambientes-con-cochera-58831047.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Fuera de Capital</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Buena Vista, San Fernando</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>USD 950</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>56 m² tot.2 amb.1 dorm.1 baño1 coch.</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclapin-lindisimo-depto-en-buena-vista-59443008.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Fuera de Capital</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Nueva Córdoba, Córdoba</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>$ 750.000</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>42 m² tot.2 amb.1 dorm.1 baño</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclapin-a-estrenar-a-m-de-ciudad-univesitaria-59349732.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Fuera de Capital</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Rosario, Santa Fe</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>$ 550.000</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>40 m² tot.2 amb.1 dorm.1 baño</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclapin-departamento-1-dor-a-50-m-de-bv-orono-59122561.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Fuera de Capital</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Nueva Córdoba, Córdoba</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>$ 1.200.000</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>75 m² tot.4 amb.2 dorm.1 baño</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclapin-departamento-amoblado-en-el-corazon-de-nueva-cordoba!-57644598.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Fuera de Capital</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>San Justo, La Matanza</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>$ 430.000</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>45 m² tot.2 amb.1 dorm.1 baño</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclapin-alquiler-depto-2-amb-san-justo-c-balcon-59668106.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Fuera de Capital</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Vicente López, GBA Norte</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>USD 2.100</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>85 m² tot.3 amb.2 dorm.2 baños1 coch.</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclapin-vicente-lopez-alquiler-departamento-3-ambientes-59318047.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Fuera de Capital</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>General Paz, Córdoba</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
           <t>$ 500.000</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>29 m² tot.2 amb.1 dorm.1 baño</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclappa-dueno-alquila-dpto-2-ambientes-lateral-super-luminoso-57250660.html</t>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>55 m² tot.2 amb.1 dorm.1 baño</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>https://www.zonaprop.com.ar/propiedades/clasificado/alclapin-alquiler-general-paz-1-dormitorio-1-bano-59659516.html</t>
         </is>
       </c>
     </row>
